--- a/docs/Mapping_casi_uso/cittadinanza/Citt_001.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_001.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="183">
   <si>
     <t>Sezione</t>
   </si>
@@ -407,79 +407,91 @@
     <t>evento.padre.recapito</t>
   </si>
   <si>
+    <t>Atto collegato di Cittadinanza</t>
+  </si>
+  <si>
+    <t>Id atto</t>
+  </si>
+  <si>
+    <t>evento.eventoCollegatoCittadinanza</t>
+  </si>
+  <si>
+    <t>idAnsc</t>
+  </si>
+  <si>
+    <t>opzionale</t>
+  </si>
+  <si>
+    <t>Provincia registrazione</t>
+  </si>
+  <si>
+    <t>idProvinciaRegistrazione</t>
+  </si>
+  <si>
+    <t>Provincia registrazione - Descrizione</t>
+  </si>
+  <si>
+    <t>siglaProvinciaRegistrazione</t>
+  </si>
+  <si>
+    <t>Comune registrazione</t>
+  </si>
+  <si>
+    <t>idComuneRegistrazione</t>
+  </si>
+  <si>
+    <t>Comune registrazione - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeComuneRegistrazione</t>
+  </si>
+  <si>
+    <t>Tipo evento</t>
+  </si>
+  <si>
+    <t>idtipocontenuto</t>
+  </si>
+  <si>
+    <t>Numero Comunale</t>
+  </si>
+  <si>
+    <t>Anno atto</t>
+  </si>
+  <si>
+    <t>annoAtto</t>
+  </si>
+  <si>
+    <t>Data atto</t>
+  </si>
+  <si>
+    <t>Parte</t>
+  </si>
+  <si>
+    <t>parte</t>
+  </si>
+  <si>
+    <t>Serie</t>
+  </si>
+  <si>
+    <t>serie</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>volume</t>
+  </si>
+  <si>
+    <t>Tipo registro</t>
+  </si>
+  <si>
+    <t>tipologia</t>
+  </si>
+  <si>
     <t>Atto nascita intestatario</t>
   </si>
   <si>
-    <t>Provincia registrazione</t>
-  </si>
-  <si>
     <t>evento.eventoCollegato</t>
-  </si>
-  <si>
-    <t>idProvinciaRegistrazione</t>
-  </si>
-  <si>
-    <t>opzionale</t>
-  </si>
-  <si>
-    <t>Provincia registrazione - Descrizione</t>
-  </si>
-  <si>
-    <t>siglaProvinciaRegistrazione</t>
-  </si>
-  <si>
-    <t>Comune registrazione</t>
-  </si>
-  <si>
-    <t>idComuneRegistrazione</t>
-  </si>
-  <si>
-    <t>Comune registrazione - Descrizione</t>
-  </si>
-  <si>
-    <t>nomeComuneRegistrazione</t>
-  </si>
-  <si>
-    <t>Tipo evento</t>
-  </si>
-  <si>
-    <t>idtipocontenuto</t>
-  </si>
-  <si>
-    <t>Numero Comunale</t>
-  </si>
-  <si>
-    <t>Anno atto</t>
-  </si>
-  <si>
-    <t>annoAtto</t>
-  </si>
-  <si>
-    <t>Data atto</t>
-  </si>
-  <si>
-    <t>Parte</t>
-  </si>
-  <si>
-    <t>parte</t>
-  </si>
-  <si>
-    <t>Serie</t>
-  </si>
-  <si>
-    <t>serie</t>
-  </si>
-  <si>
-    <t>Volume</t>
-  </si>
-  <si>
-    <t>volume</t>
-  </si>
-  <si>
-    <t>Tipo registro</t>
-  </si>
-  <si>
-    <t>tipologia</t>
   </si>
   <si>
     <t>Atto da trascrivere</t>
@@ -607,10 +619,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H142"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="22.59765625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.4296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="49.65234375" customWidth="true" bestFit="true"/>
@@ -3347,7 +3359,7 @@
         <v>133</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>17</v>
+        <v>145</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
@@ -3361,7 +3373,7 @@
         <v>131</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>38</v>
@@ -3370,7 +3382,7 @@
         <v>133</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
@@ -3393,7 +3405,7 @@
         <v>133</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>10</v>
@@ -3407,7 +3419,7 @@
         <v>131</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>38</v>
@@ -3416,7 +3428,7 @@
         <v>133</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
@@ -3496,318 +3508,318 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="C126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="F126" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>171</v>
+        <v>17</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>175</v>
+        <v>20</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>10</v>
@@ -3818,19 +3830,19 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>10</v>
@@ -3841,19 +3853,19 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>10</v>
@@ -3864,24 +3876,323 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E146" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="F146" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B153" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C142" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D142" s="2" t="s">
+      <c r="C153" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B155" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E142" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G142" s="2" t="s">
+      <c r="C155" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G155" s="2" t="s">
         <v>18</v>
       </c>
     </row>
